--- a/docs/module-checklist-by-role.xlsx
+++ b/docs/module-checklist-by-role.xlsx
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Available Credits, sale margin, request CTA</t>
+          <t xml:space="preserve">Available Credits, request CTA</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burns ~97% credits; stamps commission % of sales</t>
+          <t xml:space="preserve">Burns 100% credits; stamps commission % of sales</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Available Credits, sale margin, request CTA</t>
+          <t xml:space="preserve">Available Credits, request CTA</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burns ~97% credits; stamps commission % of sales</t>
+          <t xml:space="preserve">Burns 100% credits; stamps commission % of sales</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
